--- a/outputs/tables/psychometric_diagnostics.xlsx
+++ b/outputs/tables/psychometric_diagnostics.xlsx
@@ -8,13 +8,18 @@
   <sheets>
     <sheet name="Reliability" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Factorability" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Score_correlations" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Observed_attitude_items" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Observed_competence_items" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Factor_score_correlations" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Factor_score_p_Holm" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Factor_score_pairwise_n" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Factor_correlations_long" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
   <si>
     <t xml:space="preserve">scale</t>
   </si>
@@ -58,6 +63,12 @@
     <t xml:space="preserve">AI Literacy: Total</t>
   </si>
   <si>
+    <t xml:space="preserve">usable_items</t>
+  </si>
+  <si>
+    <t xml:space="preserve">removed_zero_variance_items</t>
+  </si>
+  <si>
     <t xml:space="preserve">kmo_overall</t>
   </si>
   <si>
@@ -79,9 +90,141 @@
     <t xml:space="preserve">GAAIS two-factor item set</t>
   </si>
   <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
     <t xml:space="preserve">AI Literacy four-factor item set</t>
   </si>
   <si>
+    <t xml:space="preserve">variable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">att_pos_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">att_pos_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">att_pos_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">att_pos_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">att_pos_7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">att_pos_11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">att_pos_12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">att_pos_13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">att_pos_14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">att_pos_16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">att_pos_17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">att_pos_18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">att_neg_3_r</t>
+  </si>
+  <si>
+    <t xml:space="preserve">att_neg_6_r</t>
+  </si>
+  <si>
+    <t xml:space="preserve">att_neg_8_r</t>
+  </si>
+  <si>
+    <t xml:space="preserve">att_neg_9_r</t>
+  </si>
+  <si>
+    <t xml:space="preserve">att_neg_10_r</t>
+  </si>
+  <si>
+    <t xml:space="preserve">att_neg_15_r</t>
+  </si>
+  <si>
+    <t xml:space="preserve">att_neg_19_r</t>
+  </si>
+  <si>
+    <t xml:space="preserve">att_neg_20_r</t>
+  </si>
+  <si>
+    <t xml:space="preserve">competence_AW_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">competence_AW_8_r</t>
+  </si>
+  <si>
+    <t xml:space="preserve">competence_AW_9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">competence_US_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">competence_US_3_r</t>
+  </si>
+  <si>
+    <t xml:space="preserve">competence_US_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">competence_EV_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">competence_EV_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">competence_EV_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">competence_ET_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">competence_ET_2_r</t>
+  </si>
+  <si>
+    <t xml:space="preserve">competence_ET_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attitude_positive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attitude_negative_favorable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attitude_favorability_index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">competence_awareness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">competence_usage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">competence_evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">competence_ethics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">competence_total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
     <t xml:space="preserve">variable_1</t>
   </si>
   <si>
@@ -95,30 +238,6 @@
   </si>
   <si>
     <t xml:space="preserve">n_pairwise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attitude_positive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attitude_negative_favorable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attitude_favorability_index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">competence_awareness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">competence_usage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">competence_evaluation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">competence_ethics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">competence_total</t>
   </si>
 </sst>
 </file>
@@ -165,6 +284,20 @@
 </styleSheet>
 </file>
 
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Table10" displayName="Table10" ref="A1:E65" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:E65"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="variable_1"/>
+    <tableColumn id="2" name="variable_2"/>
+    <tableColumn id="3" name="r"/>
+    <tableColumn id="4" name="p_holm"/>
+    <tableColumn id="5" name="n_pairwise"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:G8" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A1:G8"/>
@@ -182,32 +315,119 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:I3" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I3"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K3" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K3"/>
+  <tableColumns count="11">
     <tableColumn id="1" name="scale"/>
     <tableColumn id="2" name="n_complete"/>
     <tableColumn id="3" name="items"/>
-    <tableColumn id="4" name="kmo_overall"/>
-    <tableColumn id="5" name="bartlett_chisq"/>
-    <tableColumn id="6" name="bartlett_df"/>
-    <tableColumn id="7" name="bartlett_p"/>
-    <tableColumn id="8" name="min_item_variance"/>
-    <tableColumn id="9" name="max_absolute_item_correlation"/>
+    <tableColumn id="4" name="usable_items"/>
+    <tableColumn id="5" name="removed_zero_variance_items"/>
+    <tableColumn id="6" name="kmo_overall"/>
+    <tableColumn id="7" name="bartlett_chisq"/>
+    <tableColumn id="8" name="bartlett_df"/>
+    <tableColumn id="9" name="bartlett_p"/>
+    <tableColumn id="10" name="min_item_variance"/>
+    <tableColumn id="11" name="max_absolute_item_correlation"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:E65" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:E65"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="variable_1"/>
-    <tableColumn id="2" name="variable_2"/>
-    <tableColumn id="3" name="r"/>
-    <tableColumn id="4" name="p_holm"/>
-    <tableColumn id="5" name="n_pairwise"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:U21" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:U21"/>
+  <tableColumns count="21">
+    <tableColumn id="1" name="variable"/>
+    <tableColumn id="2" name="att_pos_1"/>
+    <tableColumn id="3" name="att_pos_2"/>
+    <tableColumn id="4" name="att_pos_4"/>
+    <tableColumn id="5" name="att_pos_5"/>
+    <tableColumn id="6" name="att_pos_7"/>
+    <tableColumn id="7" name="att_pos_11"/>
+    <tableColumn id="8" name="att_pos_12"/>
+    <tableColumn id="9" name="att_pos_13"/>
+    <tableColumn id="10" name="att_pos_14"/>
+    <tableColumn id="11" name="att_pos_16"/>
+    <tableColumn id="12" name="att_pos_17"/>
+    <tableColumn id="13" name="att_pos_18"/>
+    <tableColumn id="14" name="att_neg_3_r"/>
+    <tableColumn id="15" name="att_neg_6_r"/>
+    <tableColumn id="16" name="att_neg_8_r"/>
+    <tableColumn id="17" name="att_neg_9_r"/>
+    <tableColumn id="18" name="att_neg_10_r"/>
+    <tableColumn id="19" name="att_neg_15_r"/>
+    <tableColumn id="20" name="att_neg_19_r"/>
+    <tableColumn id="21" name="att_neg_20_r"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:M13" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:M13"/>
+  <tableColumns count="13">
+    <tableColumn id="1" name="variable"/>
+    <tableColumn id="2" name="competence_AW_1"/>
+    <tableColumn id="3" name="competence_AW_8_r"/>
+    <tableColumn id="4" name="competence_AW_9"/>
+    <tableColumn id="5" name="competence_US_1"/>
+    <tableColumn id="6" name="competence_US_3_r"/>
+    <tableColumn id="7" name="competence_US_5"/>
+    <tableColumn id="8" name="competence_EV_2"/>
+    <tableColumn id="9" name="competence_EV_3"/>
+    <tableColumn id="10" name="competence_EV_6"/>
+    <tableColumn id="11" name="competence_ET_1"/>
+    <tableColumn id="12" name="competence_ET_2_r"/>
+    <tableColumn id="13" name="competence_ET_5"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table7" displayName="Table7" ref="A1:I9" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I9"/>
+  <tableColumns count="9">
+    <tableColumn id="1" name="variable"/>
+    <tableColumn id="2" name="attitude_positive"/>
+    <tableColumn id="3" name="attitude_negative_favorable"/>
+    <tableColumn id="4" name="attitude_favorability_index"/>
+    <tableColumn id="5" name="competence_awareness"/>
+    <tableColumn id="6" name="competence_usage"/>
+    <tableColumn id="7" name="competence_evaluation"/>
+    <tableColumn id="8" name="competence_ethics"/>
+    <tableColumn id="9" name="competence_total"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Table8" displayName="Table8" ref="A1:I9" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I9"/>
+  <tableColumns count="9">
+    <tableColumn id="1" name="variable"/>
+    <tableColumn id="2" name="attitude_positive"/>
+    <tableColumn id="3" name="attitude_negative_favorable"/>
+    <tableColumn id="4" name="attitude_favorability_index"/>
+    <tableColumn id="5" name="competence_awareness"/>
+    <tableColumn id="6" name="competence_usage"/>
+    <tableColumn id="7" name="competence_evaluation"/>
+    <tableColumn id="8" name="competence_ethics"/>
+    <tableColumn id="9" name="competence_total"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Table9" displayName="Table9" ref="A1:B2" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:B2"/>
+  <tableColumns count="2">
+    <tableColumn id="1" name="variable"/>
+    <tableColumn id="2" name="value"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -705,12 +925,14 @@
     <col min="1" max="1" width="32.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="5.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="12.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="27.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="11.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="10.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="17.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="29.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="14.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="11.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="10.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="17.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="29.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -741,10 +963,16 @@
       <c r="I1" t="s">
         <v>19</v>
       </c>
+      <c r="J1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B2" t="n">
         <v>1211</v>
@@ -753,27 +981,33 @@
         <v>20</v>
       </c>
       <c r="D2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" t="n">
         <v>0.874681143514216</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>8143.4905069051</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>190</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>0.556795490374051</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>0.618750772837551</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B3" t="n">
         <v>1211</v>
@@ -782,21 +1016,27 @@
         <v>12</v>
       </c>
       <c r="D3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="n">
         <v>0.836508465500397</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>4335.52993751679</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>66</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>0.776886802110134</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>0.645536890534378</v>
       </c>
     </row>
@@ -814,6 +1054,2576 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
+    <col min="1" max="1" width="12.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="11.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="11.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="11.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="11.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="11.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="11.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="11.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="11.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="11.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="11.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="11.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="11.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="11.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="11.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="11.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="12.71" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="12.71" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="12.71" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="12.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M1" t="s">
+        <v>37</v>
+      </c>
+      <c r="N1" t="s">
+        <v>38</v>
+      </c>
+      <c r="O1" t="s">
+        <v>39</v>
+      </c>
+      <c r="P1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>41</v>
+      </c>
+      <c r="R1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S1" t="s">
+        <v>43</v>
+      </c>
+      <c r="T1" t="s">
+        <v>44</v>
+      </c>
+      <c r="U1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.267617994709331</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.373464240737937</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.00563736422623214</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.364625906536881</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.245988403020073</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.239511243543399</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.438629578998608</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.125125645024876</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.191971224492248</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.261860125559326</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.282726098124659</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-0.0909245300904354</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0119088691197831</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.0972514888674256</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.0675220071367358</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-0.00178750795550761</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.0306635518266179</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-0.0642419784580394</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-0.0400634391362532</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.267617994709331</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.359012318988912</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.31348349180546</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.450760945669591</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.4216585385591</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.420952130104246</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.290892509474291</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.403479214090501</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.283568274966144</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.407545133475838</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.449486906893983</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-0.0505341184227483</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-0.00278059367582738</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.0682265239970761</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-0.182031941763867</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.0650725759928028</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.144058618956998</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.154889262358225</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-0.0136969743390932</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.373464240737937</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.359012318988912</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.22462104829256</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.378114172691135</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.498331759097583</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.437372306526042</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.367325622700033</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.303694228616445</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.250348466378597</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.323176147199637</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.352654045027355</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-0.0438690538425746</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.0242480260247011</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.0789043166051661</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0.129883504842698</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.040281981874861</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.00698329235314718</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.0306619880485087</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-0.054445723081305</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.00563736422623214</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.31348349180546</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.22462104829256</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.281423814871974</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.332946547713808</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.405674561033174</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.0632259781492636</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.482024555947578</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.31889317510046</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.326348231839201</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.327500559609487</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.100870105983058</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-0.171553603781968</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.20833180044282</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.382372074486192</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-0.0865437312702114</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0.10738811279248</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.0050756672223278</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0.0867110693744703</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.364625906536881</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.450760945669591</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.378114172691135</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.281423814871974</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.433786846210163</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.487920513529316</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.326411678211228</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.422153035422364</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.298050769852367</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.404449475788771</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.618750772837551</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.0162299065485632</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.0759813199885096</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.059628024852285</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.200026755727208</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.111103065718771</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.174798117452758</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.102591968760771</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.0180000206151915</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.245988403020073</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.4216585385591</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.498331759097583</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.332946547713808</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.433786846210163</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.567062877710428</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.302389946470016</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.522786074958108</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.372739957127072</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.413964085909161</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.400415289018699</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.097056644412134</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.0599646327522919</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0.0369321533781659</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.248538383759619</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.0522781468616763</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.0307013155480513</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.0446578865173057</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-0.0791027257465058</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.239511243543399</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.420952130104246</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.437372306526042</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.405674561033174</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.487920513529316</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.567062877710428</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.314331766425096</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.49486555196963</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.322867481337465</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.432761709734951</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.458983742600734</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-0.102086511034369</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-0.0656824468365302</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0.0225662526114699</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.25348672484319</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.00144698776957443</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.0391946586709385</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.0533671027248916</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0.0480961803031285</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.438629578998608</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.290892509474291</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.367325622700033</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0632259781492636</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.326411678211228</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.302389946470016</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.314331766425096</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.18185649104221</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.38966564923567</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.262888558245962</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.357632903272096</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.0889149815380037</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0389811267506459</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.0917117039771628</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-0.0275722413762485</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.0227816073067808</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.0760009124800399</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.0145272744310159</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0.0836672425746098</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.125125645024876</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.403479214090501</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.303694228616445</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.482024555947578</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.422153035422364</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.522786074958108</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.49486555196963</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.18185649104221</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.39604915868766</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.466444091045808</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.473730161189649</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.0164426015518299</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.182106909390263</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.115949492880849</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.361984416381807</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.0107832276259224</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.0104528264236228</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.098434953225108</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.0182524028691299</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.191971224492248</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.283568274966144</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.250348466378597</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.31889317510046</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.298050769852367</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.372739957127072</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.322867481337465</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.38966564923567</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.39604915868766</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.372299977593589</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.326392780472176</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.126060130331798</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-0.0533057062605102</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0.10286286397957</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-0.270930624670304</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0.0870918775018962</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.0843289289068786</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.0609851754726475</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.161984816043065</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.261860125559326</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.407545133475838</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.323176147199637</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.326348231839201</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.404449475788771</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.413964085909161</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.432761709734951</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.262888558245962</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.466444091045808</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.372299977593589</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.515003241882722</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-0.0649802896589368</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.00227577107521508</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.0370498523863257</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-0.148151880414309</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.076534198694342</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.116636889045827</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.0328052490127025</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.0142128976356099</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.282726098124659</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.449486906893983</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.352654045027355</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.327500559609487</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.618750772837551</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.400415289018699</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.458983742600734</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.357632903272096</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.473730161189649</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.326392780472176</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.515003241882722</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.0141428272384644</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-0.0105775861029175</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.0458880553096715</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0.136606856822895</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.122797583140932</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.204651770929092</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.155993751846159</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.0383109053122634</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-0.0909245300904354</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.0505341184227483</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.0438690538425746</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.100870105983058</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.0162299065485632</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.097056644412134</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.102086511034369</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0.0889149815380037</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-0.0164426015518299</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0.126060130331798</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-0.0649802896589368</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.0141428272384644</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.274105600500309</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.351945458310537</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.276868047533365</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.337210641905284</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.253284751739668</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.213852703721672</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.280063085830583</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.0119088691197831</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.00278059367582738</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.0242480260247011</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.171553603781968</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.0759813199885096</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.0599646327522919</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.0656824468365302</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.0389811267506459</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-0.182106909390263</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0.0533057062605102</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.00227577107521508</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-0.0105775861029175</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.274105600500309</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.391951359443357</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.302487337782907</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.314560899496195</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.193614433406725</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.230205596114879</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.165627497675658</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.0972514888674256</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.0682265239970761</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.0789043166051661</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.20833180044282</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.059628024852285</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.0369321533781659</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.0225662526114699</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.0917117039771628</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-0.115949492880849</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0.10286286397957</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.0370498523863257</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.0458880553096715</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.351945458310537</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.391951359443357</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.488614309235571</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.549400058672777</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.398936384490501</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.232728664876214</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.267997377192801</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.0675220071367358</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.182031941763867</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.129883504842698</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.382372074486192</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-0.200026755727208</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.248538383759619</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.25348672484319</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-0.0275722413762485</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-0.361984416381807</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-0.270930624670304</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-0.148151880414309</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-0.136606856822895</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.276868047533365</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.302487337782907</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.488614309235571</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.371004023348765</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.224785000815122</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.111051796181666</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.209742950913838</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-0.00178750795550761</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.0650725759928028</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.040281981874861</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.0865437312702114</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.111103065718771</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.0522781468616763</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.00144698776957443</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.0227816073067808</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.0107832276259224</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0.0870918775018962</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.076534198694342</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.122797583140932</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.337210641905284</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.314560899496195</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.549400058672777</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.371004023348765</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.466853533869262</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.344658266600274</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.351668948492143</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0.0306635518266179</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.144058618956998</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.00698329235314718</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.10738811279248</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.174798117452758</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.0307013155480513</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.0391946586709385</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.0760009124800399</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.0104528264236228</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-0.0843289289068786</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.116636889045827</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.204651770929092</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.253284751739668</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.193614433406725</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.398936384490501</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.224785000815122</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.466853533869262</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.449918130082344</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.313176984067065</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-0.0642419784580394</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.154889262358225</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.0306619880485087</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.0050756672223278</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.102591968760771</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.0446578865173057</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.0533671027248916</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-0.0145272744310159</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.098434953225108</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-0.0609851754726475</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.0328052490127025</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.155993751846159</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.213852703721672</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.230205596114879</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.232728664876214</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.111051796181666</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.344658266600274</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.449918130082344</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.327398940980462</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-0.0400634391362532</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.0136969743390932</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.054445723081305</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-0.0867110693744703</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0.0180000206151915</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-0.0791027257465058</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.0480961803031285</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-0.0836672425746098</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.0182524028691299</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-0.161984816043065</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.0142128976356099</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.0383109053122634</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.280063085830583</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.165627497675658</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.267997377192801</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.209742950913838</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.351668948492143</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.313176984067065</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.327398940980462</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId5"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="17.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="15.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="17.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="15.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="15.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="17.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="15.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="15.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="15.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="15.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="15.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="17.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="15.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L1" t="s">
+        <v>56</v>
+      </c>
+      <c r="M1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.149029319187789</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.457508379926087</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.37046900393905</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.208606849637576</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.254798189732074</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.436182608530502</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.32496248088319</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.45089187637055</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.242988291007562</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-0.0483327250702426</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.301937321834856</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-0.149029319187789</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.101108715934067</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.297596229813512</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.44754669217044</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.334793754793052</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.179940502910901</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-0.260895034702212</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-0.197714558375127</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-0.0677116908944671</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.137110609356486</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-0.0155727366020519</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.457508379926087</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.101108715934067</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.37877029683852</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.122728438923987</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.277345063243243</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.57764259989121</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.274559789588428</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.489796903584521</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.263935327341455</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0191271677041449</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.427465359908782</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.37046900393905</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.297596229813512</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.37877029683852</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.17690557851586</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.645536890534378</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.434306843583534</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.434674594705569</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.50548199651497</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.232600687812317</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.150197456361309</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.245944250456197</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-0.208606849637576</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.44754669217044</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.122728438923987</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.17690557851586</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.116136091513795</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.154017044241559</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-0.0769069606457822</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-0.15750918180599</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0.0320424677337021</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.137601066955604</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-0.0224800025089799</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.254798189732074</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.334793754793052</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.277345063243243</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.645536890534378</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.116136091513795</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.347353111784276</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.479420697450724</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.444894111959486</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.296104876868089</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0927417103993887</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.177688525862042</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.436182608530502</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.179940502910901</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.57764259989121</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.434306843583534</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.154017044241559</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.347353111784276</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.37843446284281</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.542305452739514</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.26453883728348</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0530016330429033</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.382458081420708</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.32496248088319</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.260895034702212</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.274559789588428</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.434674594705569</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.0769069606457822</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.479420697450724</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.37843446284281</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.399290406902542</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.418720566432591</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.102630213200542</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.300516760604275</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.45089187637055</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.197714558375127</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.489796903584521</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.50548199651497</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.15750918180599</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.444894111959486</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.542305452739514</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.399290406902542</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.244372246406736</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0731501977229881</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.342918718135176</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.242988291007562</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.0677116908944671</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.263935327341455</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.232600687812317</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.0320424677337021</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.296104876868089</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.26453883728348</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.418720566432591</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.244372246406736</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.0917246173196838</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.350322848366765</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-0.0483327250702426</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.137110609356486</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.0191271677041449</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.150197456361309</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.137601066955604</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0927417103993887</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.0530016330429033</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.102630213200542</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.0731501977229881</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-0.0917246173196838</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0.0421817110970289</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.301937321834856</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.0155727366020519</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.427465359908782</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.245944250456197</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.0224800025089799</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.177688525862042</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.382458081420708</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.300516760604275</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.342918718135176</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.350322848366765</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0.0421817110970289</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId6"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="27.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="17.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="27.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="27.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="20.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="16.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="21.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="17.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="16.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.0422258129968075</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.822090116003482</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.249932726770631</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.480641275836943</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.402521982423363</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.245789870611451</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.491263231724979</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-0.0422258129968075</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.534136155608582</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.215129457140626</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.0712864749510076</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.0468050517964131</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.138574421881916</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-0.162979145730307</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.822090116003482</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.534136155608582</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.0888864755470457</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.366072418709504</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.31392265435685</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.12900707046776</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.322807715812227</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.249932726770631</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.215129457140626</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.0888864755470457</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.191453717408593</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.373608718546554</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.295653468570672</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.646717388135207</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.480641275836943</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.0712864749510076</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.366072418709504</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.191453717408593</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.421764945171663</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.296192385966366</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.679939053356186</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.402521982423363</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.0468050517964131</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.31392265435685</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.373608718546554</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.421764945171663</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.400412881685803</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.791921035390237</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.245789870611451</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.138574421881916</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.12900707046776</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.295653468570672</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.296192385966366</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.400412881685803</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.701572333534976</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.491263231724979</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.162979145730307</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.322807715812227</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.646717388135207</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.679939053356186</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.791921035390237</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.701572333534976</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId7"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="27.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="17.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="27.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="27.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="20.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="16.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="21.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="17.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="16.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.20705014824233</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.42274089719385e-296</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0000000000000000116154441857012</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000108854760506438</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0000000000000000000000000000000000000000000000422934258078632</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.000000000000000040287916926136</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000315719216121175</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.141949034682831</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000647320220737097</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.000000000000342625523567185</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.0392686222478805</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.20705014824233</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.00000776286694184664</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.0000000819672930576731</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5.08121748997804e-298</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000028144357423352</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.00784246959517455</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.000000000000000000000000000000000000016816484589351</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.000000000000000000000000000588426869016001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.0000334111675754961</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.0000000000000000000000000000136435051826395</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.00000000000000000105594947142738</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.0000000000000380695026185761</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.00196061739879364</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.00000000014755606657363</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.00000000000000000000000000000000000000035311887805645</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.000000000000000000000000894854707476116</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000519723952324398</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000518356002411612</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0130895407492935</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.00000000000000000000000000000000000000105103028683444</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.0000000000184445083217038</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.00000000000000000000000000000000000000000000000000040877186536419</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.000000000000000000000000783367652610398</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000106852813860862</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.00000000000000000000000000000000000000000000000222596977936122</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.103525074121165</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.000000000000000000000000000042030490644</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.0000000000000000000000000000000000000000207716987092029</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.0000000000000000000000000000000000000000000000000000204385932682095</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.000000000000000000000000000000000000000000000136478884788587</v>
+      </c>
+      <c r="I7" t="n">
+        <v>7.82159370177913e-260</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.0000000000000000040287916926136</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.00000129381115697444</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.00000668223351509922</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.0000000000000000000000000745712256230097</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.0000000000000000000000000602590502007998</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.00000000000000000000000000000000000000000000000758216026603264</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000104344773940802</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000143508734600534</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0000000117096132939533</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.000000000000000000000000000000909567012175963</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000216551646801832</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000427411255443446</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.89688655621449e-261</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000401326053618469</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId8"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="8.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="5.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1211</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId9"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
     <col min="1" max="1" width="27.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="27.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="11.71" hidden="0" customWidth="1"/>
@@ -823,27 +3633,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="B1" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="C1" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="D1" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="E1" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -857,10 +3667,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="C3" t="n">
         <v>-0.0422258129968075</v>
@@ -874,10 +3684,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="C4" t="n">
         <v>0.822090116003482</v>
@@ -891,10 +3701,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="C5" t="n">
         <v>0.249932726770631</v>
@@ -908,10 +3718,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="C6" t="n">
         <v>0.480641275836943</v>
@@ -925,10 +3735,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="C7" t="n">
         <v>0.402521982423363</v>
@@ -942,10 +3752,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
         <v>0.245789870611451</v>
@@ -959,10 +3769,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="C9" t="n">
         <v>0.491263231724979</v>
@@ -976,10 +3786,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="C10" t="n">
         <v>-0.0422258129968075</v>
@@ -993,10 +3803,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
@@ -1010,10 +3820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="C12" t="n">
         <v>0.534136155608582</v>
@@ -1027,10 +3837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="C13" t="n">
         <v>-0.215129457140626</v>
@@ -1044,10 +3854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="C14" t="n">
         <v>-0.0712864749510076</v>
@@ -1061,10 +3871,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="C15" t="n">
         <v>-0.0468050517964131</v>
@@ -1078,10 +3888,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="C16" t="n">
         <v>-0.138574421881916</v>
@@ -1095,10 +3905,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="C17" t="n">
         <v>-0.162979145730307</v>
@@ -1112,10 +3922,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="C18" t="n">
         <v>0.822090116003482</v>
@@ -1129,10 +3939,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="C19" t="n">
         <v>0.534136155608582</v>
@@ -1146,10 +3956,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>
@@ -1163,10 +3973,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="C21" t="n">
         <v>0.0888864755470457</v>
@@ -1180,10 +3990,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="B22" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="C22" t="n">
         <v>0.366072418709504</v>
@@ -1197,10 +4007,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="B23" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="C23" t="n">
         <v>0.31392265435685</v>
@@ -1214,10 +4024,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="B24" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="C24" t="n">
         <v>0.12900707046776</v>
@@ -1231,10 +4041,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="C25" t="n">
         <v>0.322807715812227</v>
@@ -1248,10 +4058,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="B26" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="C26" t="n">
         <v>0.249932726770631</v>
@@ -1265,10 +4075,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="C27" t="n">
         <v>-0.215129457140626</v>
@@ -1282,10 +4092,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="B28" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="C28" t="n">
         <v>0.0888864755470457</v>
@@ -1299,10 +4109,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="B29" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
@@ -1316,10 +4126,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="C30" t="n">
         <v>0.191453717408593</v>
@@ -1333,10 +4143,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="B31" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="C31" t="n">
         <v>0.373608718546554</v>
@@ -1350,10 +4160,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="B32" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="C32" t="n">
         <v>0.295653468570672</v>
@@ -1367,10 +4177,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="B33" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="C33" t="n">
         <v>0.646717388135207</v>
@@ -1384,10 +4194,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="B34" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="C34" t="n">
         <v>0.480641275836943</v>
@@ -1401,10 +4211,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="B35" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="C35" t="n">
         <v>-0.0712864749510076</v>
@@ -1418,10 +4228,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="B36" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="C36" t="n">
         <v>0.366072418709504</v>
@@ -1435,10 +4245,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="B37" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="C37" t="n">
         <v>0.191453717408593</v>
@@ -1452,10 +4262,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="B38" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="C38" t="n">
         <v>1</v>
@@ -1469,10 +4279,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="B39" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="C39" t="n">
         <v>0.421764945171663</v>
@@ -1486,10 +4296,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="B40" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="C40" t="n">
         <v>0.296192385966366</v>
@@ -1503,10 +4313,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="B41" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="C41" t="n">
         <v>0.679939053356186</v>
@@ -1520,10 +4330,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="B42" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="C42" t="n">
         <v>0.402521982423363</v>
@@ -1537,10 +4347,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="B43" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="C43" t="n">
         <v>-0.0468050517964131</v>
@@ -1554,10 +4364,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="B44" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="C44" t="n">
         <v>0.31392265435685</v>
@@ -1571,10 +4381,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="B45" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="C45" t="n">
         <v>0.373608718546554</v>
@@ -1588,10 +4398,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="B46" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="C46" t="n">
         <v>0.421764945171663</v>
@@ -1605,10 +4415,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="B47" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="C47" t="n">
         <v>1</v>
@@ -1622,10 +4432,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="B48" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="C48" t="n">
         <v>0.400412881685803</v>
@@ -1639,10 +4449,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="B49" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="C49" t="n">
         <v>0.791921035390237</v>
@@ -1656,10 +4466,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="B50" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="C50" t="n">
         <v>0.245789870611451</v>
@@ -1673,10 +4483,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="B51" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="C51" t="n">
         <v>-0.138574421881916</v>
@@ -1690,10 +4500,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="B52" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="C52" t="n">
         <v>0.12900707046776</v>
@@ -1707,10 +4517,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="B53" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="C53" t="n">
         <v>0.295653468570672</v>
@@ -1724,10 +4534,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="B54" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="C54" t="n">
         <v>0.296192385966366</v>
@@ -1741,10 +4551,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="B55" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="C55" t="n">
         <v>0.400412881685803</v>
@@ -1758,10 +4568,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="B56" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="C56" t="n">
         <v>1</v>
@@ -1775,10 +4585,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="B57" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="C57" t="n">
         <v>0.701572333534976</v>
@@ -1792,10 +4602,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="B58" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="C58" t="n">
         <v>0.491263231724979</v>
@@ -1809,10 +4619,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="B59" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="C59" t="n">
         <v>-0.162979145730307</v>
@@ -1826,10 +4636,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="B60" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="C60" t="n">
         <v>0.322807715812227</v>
@@ -1843,10 +4653,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="B61" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="C61" t="n">
         <v>0.646717388135207</v>
@@ -1860,10 +4670,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="B62" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="C62" t="n">
         <v>0.679939053356186</v>
@@ -1877,10 +4687,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="B63" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="C63" t="n">
         <v>0.791921035390237</v>
@@ -1894,10 +4704,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="B64" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="C64" t="n">
         <v>0.701572333534976</v>
@@ -1911,10 +4721,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="B65" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="C65" t="n">
         <v>1</v>
@@ -1930,7 +4740,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId10"/>
   </tableParts>
 </worksheet>
 </file>
--- a/outputs/tables/psychometric_diagnostics.xlsx
+++ b/outputs/tables/psychometric_diagnostics.xlsx
@@ -8,18 +8,21 @@
   <sheets>
     <sheet name="Reliability" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Factorability" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Observed_attitude_items" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Observed_competence_items" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Factor_score_correlations" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Factor_score_p_Holm" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Factor_score_pairwise_n" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Factor_correlations_long" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Parallel_analysis" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Factor_score_diagnostics" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Excluded_factor_scores" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Observed_attitude_items" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Observed_competence_items" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Factor_score_correlations" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Factor_score_p_Holm" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Factor_score_pairwise_n" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Factor_correlations_long" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="98">
   <si>
     <t xml:space="preserve">scale</t>
   </si>
@@ -69,6 +72,9 @@
     <t xml:space="preserve">removed_zero_variance_items</t>
   </si>
   <si>
+    <t xml:space="preserve">missing_items</t>
+  </si>
+  <si>
     <t xml:space="preserve">kmo_overall</t>
   </si>
   <si>
@@ -87,18 +93,90 @@
     <t xml:space="preserve">max_absolute_item_correlation</t>
   </si>
   <si>
+    <t xml:space="preserve">status</t>
+  </si>
+  <si>
     <t xml:space="preserve">GAAIS two-factor item set</t>
   </si>
   <si>
     <t xml:space="preserve"/>
   </si>
   <si>
+    <t xml:space="preserve">Estimated</t>
+  </si>
+  <si>
     <t xml:space="preserve">AI Literacy four-factor item set</t>
   </si>
   <si>
+    <t xml:space="preserve">suggested_factors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">suggested_components</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAAIS attitudes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Literacy</t>
+  </si>
+  <si>
     <t xml:space="preserve">variable</t>
   </si>
   <si>
+    <t xml:space="preserve">n_total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_nonmissing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_missing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">missing_pct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique_nonmissing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">variance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">usable_for_correlation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exclusion_reason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attitude_positive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attitude_negative_concern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attitude_negative_favorable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">competence_awareness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">competence_usage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">competence_evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">competence_ethics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">competence_total</t>
+  </si>
+  <si>
     <t xml:space="preserve">att_pos_1</t>
   </si>
   <si>
@@ -195,36 +273,6 @@
     <t xml:space="preserve">competence_ET_5</t>
   </si>
   <si>
-    <t xml:space="preserve">attitude_positive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attitude_negative_favorable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attitude_favorability_index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">competence_awareness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">competence_usage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">competence_evaluation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">competence_ethics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">competence_total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
     <t xml:space="preserve">variable_1</t>
   </si>
   <si>
@@ -238,6 +286,36 @@
   </si>
   <si>
     <t xml:space="preserve">n_pairwise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">absolute_r</t>
+  </si>
+  <si>
+    <t xml:space="preserve">direction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">magnitude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">significant_holm_05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Large</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Negligible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Negative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Small</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moderate</t>
   </si>
 </sst>
 </file>
@@ -285,14 +363,72 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Table10" displayName="Table10" ref="A1:E65" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:E65"/>
-  <tableColumns count="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Table10" displayName="Table10" ref="A1:I9" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I9"/>
+  <tableColumns count="9">
+    <tableColumn id="1" name="variable"/>
+    <tableColumn id="2" name="attitude_positive"/>
+    <tableColumn id="3" name="attitude_negative_concern"/>
+    <tableColumn id="4" name="attitude_negative_favorable"/>
+    <tableColumn id="5" name="competence_awareness"/>
+    <tableColumn id="6" name="competence_usage"/>
+    <tableColumn id="7" name="competence_evaluation"/>
+    <tableColumn id="8" name="competence_ethics"/>
+    <tableColumn id="9" name="competence_total"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Table11" displayName="Table11" ref="A1:I9" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I9"/>
+  <tableColumns count="9">
+    <tableColumn id="1" name="variable"/>
+    <tableColumn id="2" name="attitude_positive"/>
+    <tableColumn id="3" name="attitude_negative_concern"/>
+    <tableColumn id="4" name="attitude_negative_favorable"/>
+    <tableColumn id="5" name="competence_awareness"/>
+    <tableColumn id="6" name="competence_usage"/>
+    <tableColumn id="7" name="competence_evaluation"/>
+    <tableColumn id="8" name="competence_ethics"/>
+    <tableColumn id="9" name="competence_total"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Table12" displayName="Table12" ref="A1:I9" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I9"/>
+  <tableColumns count="9">
+    <tableColumn id="1" name="variable"/>
+    <tableColumn id="2" name="attitude_positive"/>
+    <tableColumn id="3" name="attitude_negative_concern"/>
+    <tableColumn id="4" name="attitude_negative_favorable"/>
+    <tableColumn id="5" name="competence_awareness"/>
+    <tableColumn id="6" name="competence_usage"/>
+    <tableColumn id="7" name="competence_evaluation"/>
+    <tableColumn id="8" name="competence_ethics"/>
+    <tableColumn id="9" name="competence_total"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="Table13" displayName="Table13" ref="A1:I65" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I65"/>
+  <tableColumns count="9">
     <tableColumn id="1" name="variable_1"/>
     <tableColumn id="2" name="variable_2"/>
     <tableColumn id="3" name="r"/>
     <tableColumn id="4" name="p_holm"/>
     <tableColumn id="5" name="n_pairwise"/>
+    <tableColumn id="6" name="absolute_r"/>
+    <tableColumn id="7" name="direction"/>
+    <tableColumn id="8" name="magnitude"/>
+    <tableColumn id="9" name="significant_holm_05"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -315,27 +451,82 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K3" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K3"/>
-  <tableColumns count="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:M3" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:M3"/>
+  <tableColumns count="13">
     <tableColumn id="1" name="scale"/>
     <tableColumn id="2" name="n_complete"/>
     <tableColumn id="3" name="items"/>
     <tableColumn id="4" name="usable_items"/>
     <tableColumn id="5" name="removed_zero_variance_items"/>
-    <tableColumn id="6" name="kmo_overall"/>
-    <tableColumn id="7" name="bartlett_chisq"/>
-    <tableColumn id="8" name="bartlett_df"/>
-    <tableColumn id="9" name="bartlett_p"/>
-    <tableColumn id="10" name="min_item_variance"/>
-    <tableColumn id="11" name="max_absolute_item_correlation"/>
+    <tableColumn id="6" name="missing_items"/>
+    <tableColumn id="7" name="kmo_overall"/>
+    <tableColumn id="8" name="bartlett_chisq"/>
+    <tableColumn id="9" name="bartlett_df"/>
+    <tableColumn id="10" name="bartlett_p"/>
+    <tableColumn id="11" name="min_item_variance"/>
+    <tableColumn id="12" name="max_absolute_item_correlation"/>
+    <tableColumn id="13" name="status"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:U21" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:D3" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:D3"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="scale"/>
+    <tableColumn id="2" name="suggested_factors"/>
+    <tableColumn id="3" name="suggested_components"/>
+    <tableColumn id="4" name="status"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:K9" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K9"/>
+  <tableColumns count="11">
+    <tableColumn id="1" name="variable"/>
+    <tableColumn id="2" name="n_total"/>
+    <tableColumn id="3" name="n_nonmissing"/>
+    <tableColumn id="4" name="n_missing"/>
+    <tableColumn id="5" name="missing_pct"/>
+    <tableColumn id="6" name="unique_nonmissing"/>
+    <tableColumn id="7" name="mean"/>
+    <tableColumn id="8" name="sd"/>
+    <tableColumn id="9" name="variance"/>
+    <tableColumn id="10" name="usable_for_correlation"/>
+    <tableColumn id="11" name="exclusion_reason"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table7" displayName="Table7" ref="A1:K2" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K2"/>
+  <tableColumns count="11">
+    <tableColumn id="1" name="variable"/>
+    <tableColumn id="2" name="n_total"/>
+    <tableColumn id="3" name="n_nonmissing"/>
+    <tableColumn id="4" name="n_missing"/>
+    <tableColumn id="5" name="missing_pct"/>
+    <tableColumn id="6" name="unique_nonmissing"/>
+    <tableColumn id="7" name="mean"/>
+    <tableColumn id="8" name="sd"/>
+    <tableColumn id="9" name="variance"/>
+    <tableColumn id="10" name="usable_for_correlation"/>
+    <tableColumn id="11" name="exclusion_reason"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Table8" displayName="Table8" ref="A1:U21" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A1:U21"/>
   <tableColumns count="21">
     <tableColumn id="1" name="variable"/>
@@ -364,8 +555,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:M13" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Table9" displayName="Table9" ref="A1:M13" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A1:M13"/>
   <tableColumns count="13">
     <tableColumn id="1" name="variable"/>
@@ -381,53 +572,6 @@
     <tableColumn id="11" name="competence_ET_1"/>
     <tableColumn id="12" name="competence_ET_2_r"/>
     <tableColumn id="13" name="competence_ET_5"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table7" displayName="Table7" ref="A1:I9" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I9"/>
-  <tableColumns count="9">
-    <tableColumn id="1" name="variable"/>
-    <tableColumn id="2" name="attitude_positive"/>
-    <tableColumn id="3" name="attitude_negative_favorable"/>
-    <tableColumn id="4" name="attitude_favorability_index"/>
-    <tableColumn id="5" name="competence_awareness"/>
-    <tableColumn id="6" name="competence_usage"/>
-    <tableColumn id="7" name="competence_evaluation"/>
-    <tableColumn id="8" name="competence_ethics"/>
-    <tableColumn id="9" name="competence_total"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Table8" displayName="Table8" ref="A1:I9" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I9"/>
-  <tableColumns count="9">
-    <tableColumn id="1" name="variable"/>
-    <tableColumn id="2" name="attitude_positive"/>
-    <tableColumn id="3" name="attitude_negative_favorable"/>
-    <tableColumn id="4" name="attitude_favorability_index"/>
-    <tableColumn id="5" name="competence_awareness"/>
-    <tableColumn id="6" name="competence_usage"/>
-    <tableColumn id="7" name="competence_evaluation"/>
-    <tableColumn id="8" name="competence_ethics"/>
-    <tableColumn id="9" name="competence_total"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Table9" displayName="Table9" ref="A1:B2" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:B2"/>
-  <tableColumns count="2">
-    <tableColumn id="1" name="variable"/>
-    <tableColumn id="2" name="value"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -804,16 +948,16 @@
         <v>1211</v>
       </c>
       <c r="D4" t="n">
-        <v>0.16927087213258</v>
+        <v>0.383874384041521</v>
       </c>
       <c r="E4" t="n">
-        <v>0.200349841986843</v>
+        <v>0.399294422196308</v>
       </c>
       <c r="F4" t="n">
         <v>0.467750853391886</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0770783740345666</v>
+        <v>0.181381120550441</v>
       </c>
     </row>
     <row r="5">
@@ -827,16 +971,16 @@
         <v>1211</v>
       </c>
       <c r="D5" t="n">
-        <v>0.240473918551389</v>
+        <v>0.492191003573962</v>
       </c>
       <c r="E5" t="n">
-        <v>0.28053680392993</v>
+        <v>0.513037448388037</v>
       </c>
       <c r="F5" t="n">
         <v>0.634231823589298</v>
       </c>
       <c r="G5" t="n">
-        <v>0.115024711214741</v>
+        <v>0.259907251572066</v>
       </c>
     </row>
     <row r="6">
@@ -873,16 +1017,16 @@
         <v>1211</v>
       </c>
       <c r="D7" t="n">
-        <v>0.113094759790238</v>
+        <v>0.273732898258086</v>
       </c>
       <c r="E7" t="n">
-        <v>0.157938808098131</v>
+        <v>0.302715058116095</v>
       </c>
       <c r="F7" t="n">
         <v>0.368349281875884</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0588418803297305</v>
+        <v>0.126417299477507</v>
       </c>
     </row>
     <row r="8">
@@ -896,16 +1040,16 @@
         <v>1211</v>
       </c>
       <c r="D8" t="n">
-        <v>0.656889608164138</v>
+        <v>0.737048919197393</v>
       </c>
       <c r="E8" t="n">
-        <v>0.685746915060903</v>
+        <v>0.754924648476059</v>
       </c>
       <c r="F8" t="n">
         <v>0.766314038121994</v>
       </c>
       <c r="G8" t="n">
-        <v>0.153865864974669</v>
+        <v>0.204263962345526</v>
       </c>
     </row>
   </sheetData>
@@ -913,6 +1057,2202 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <tableParts count="1">
     <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="27.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="17.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="25.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="27.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="20.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="16.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="21.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="17.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="16.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1211</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1211</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1211</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1211</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1211</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1211</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1211</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1211</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1211</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1211</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1211</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1211</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1211</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1211</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1211</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1211</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1211</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1211</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1211</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1211</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1211</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1211</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1211</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1211</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1211</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1211</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1211</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1211</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1211</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1211</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1211</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1211</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1211</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId12"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="27.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="27.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="11.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="10.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="11.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="9.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="10.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="19.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.0422258129968075</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.141949034682831</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.0422258129968075</v>
+      </c>
+      <c r="G3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.0422258129968075</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.141949034682831</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.0422258129968075</v>
+      </c>
+      <c r="G4" t="s">
+        <v>95</v>
+      </c>
+      <c r="H4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.290214849324628</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.000000000000000000000000624481068378737</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.290214849324628</v>
+      </c>
+      <c r="G5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H5" t="s">
+        <v>96</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.386808795276402</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.0000000000000000000000000000000000000000000166680454063474</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.386808795276402</v>
+      </c>
+      <c r="G6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.402521982423363</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.00000000000000000000000000000000000000000000000222596977936122</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.402521982423363</v>
+      </c>
+      <c r="G7" t="s">
+        <v>92</v>
+      </c>
+      <c r="H7" t="s">
+        <v>97</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.0577676923179115</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.0444433580927909</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.0577676923179115</v>
+      </c>
+      <c r="G8" t="s">
+        <v>92</v>
+      </c>
+      <c r="H8" t="s">
+        <v>94</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.390859735670668</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.00000000000000000000000000000000000000000000174999899645839</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.390859735670668</v>
+      </c>
+      <c r="G9" t="s">
+        <v>92</v>
+      </c>
+      <c r="H9" t="s">
+        <v>97</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0422258129968075</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.828200592969321</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.0422258129968075</v>
+      </c>
+      <c r="G10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H10" t="s">
+        <v>94</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>92</v>
+      </c>
+      <c r="H11" t="s">
+        <v>93</v>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="s">
+        <v>95</v>
+      </c>
+      <c r="H12" t="s">
+        <v>93</v>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.0441310527305925</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.124809100054632</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.0441310527305925</v>
+      </c>
+      <c r="G13" t="s">
+        <v>95</v>
+      </c>
+      <c r="H13" t="s">
+        <v>94</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.101894702048812</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.000383096928911812</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.101894702048812</v>
+      </c>
+      <c r="G14" t="s">
+        <v>95</v>
+      </c>
+      <c r="H14" t="s">
+        <v>96</v>
+      </c>
+      <c r="I14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.0468050517964131</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.103525074121165</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.0468050517964131</v>
+      </c>
+      <c r="G15" t="s">
+        <v>92</v>
+      </c>
+      <c r="H15" t="s">
+        <v>94</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.0577599479280523</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.0444719380127927</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.0577599479280523</v>
+      </c>
+      <c r="G16" t="s">
+        <v>92</v>
+      </c>
+      <c r="H16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.0157149574167822</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.584831921900787</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.0157149574167822</v>
+      </c>
+      <c r="G17" t="s">
+        <v>95</v>
+      </c>
+      <c r="H17" t="s">
+        <v>94</v>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.0422258129968075</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.828200592969321</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.0422258129968075</v>
+      </c>
+      <c r="G18" t="s">
+        <v>95</v>
+      </c>
+      <c r="H18" t="s">
+        <v>94</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="s">
+        <v>95</v>
+      </c>
+      <c r="H19" t="s">
+        <v>93</v>
+      </c>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="s">
+        <v>92</v>
+      </c>
+      <c r="H20" t="s">
+        <v>93</v>
+      </c>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.0441310527305925</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.124809100054632</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.0441310527305925</v>
+      </c>
+      <c r="G21" t="s">
+        <v>92</v>
+      </c>
+      <c r="H21" t="s">
+        <v>94</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.101894702048812</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.000383096928911812</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.101894702048812</v>
+      </c>
+      <c r="G22" t="s">
+        <v>92</v>
+      </c>
+      <c r="H22" t="s">
+        <v>96</v>
+      </c>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.0468050517964131</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.103525074121165</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.0468050517964131</v>
+      </c>
+      <c r="G23" t="s">
+        <v>95</v>
+      </c>
+      <c r="H23" t="s">
+        <v>94</v>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.0577599479280523</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.0444719380127927</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.0577599479280523</v>
+      </c>
+      <c r="G24" t="s">
+        <v>95</v>
+      </c>
+      <c r="H24" t="s">
+        <v>94</v>
+      </c>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.0157149574167822</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.584831921900787</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.0157149574167822</v>
+      </c>
+      <c r="G25" t="s">
+        <v>92</v>
+      </c>
+      <c r="H25" t="s">
+        <v>94</v>
+      </c>
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.290214849324628</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.0000000000000000000000106161781624385</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.290214849324628</v>
+      </c>
+      <c r="G26" t="s">
+        <v>92</v>
+      </c>
+      <c r="H26" t="s">
+        <v>96</v>
+      </c>
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.0441310527305925</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.828200592969321</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.0441310527305925</v>
+      </c>
+      <c r="G27" t="s">
+        <v>95</v>
+      </c>
+      <c r="H27" t="s">
+        <v>94</v>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.0441310527305925</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.828200592969321</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.0441310527305925</v>
+      </c>
+      <c r="G28" t="s">
+        <v>92</v>
+      </c>
+      <c r="H28" t="s">
+        <v>94</v>
+      </c>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="s">
+        <v>92</v>
+      </c>
+      <c r="H29" t="s">
+        <v>93</v>
+      </c>
+      <c r="I29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.501899133337645</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000292827451124057</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.501899133337645</v>
+      </c>
+      <c r="G30" t="s">
+        <v>92</v>
+      </c>
+      <c r="H30" t="s">
+        <v>93</v>
+      </c>
+      <c r="I30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.561102867268935</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000223074973983556</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.561102867268935</v>
+      </c>
+      <c r="G31" t="s">
+        <v>92</v>
+      </c>
+      <c r="H31" t="s">
+        <v>93</v>
+      </c>
+      <c r="I31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.28597019957759</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.00000000000000000000000317677727517376</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.28597019957759</v>
+      </c>
+      <c r="G32" t="s">
+        <v>92</v>
+      </c>
+      <c r="H32" t="s">
+        <v>96</v>
+      </c>
+      <c r="I32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>50</v>
+      </c>
+      <c r="B33" t="s">
+        <v>46</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.796541000136099</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1.74083967244778e-266</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.796541000136099</v>
+      </c>
+      <c r="G33" t="s">
+        <v>92</v>
+      </c>
+      <c r="H33" t="s">
+        <v>93</v>
+      </c>
+      <c r="I33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.386808795276402</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.000000000000000000000000000000000000000000300024817314252</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.386808795276402</v>
+      </c>
+      <c r="G34" t="s">
+        <v>92</v>
+      </c>
+      <c r="H34" t="s">
+        <v>97</v>
+      </c>
+      <c r="I34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" t="s">
+        <v>47</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-0.101894702048812</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.00498026007585355</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.101894702048812</v>
+      </c>
+      <c r="G35" t="s">
+        <v>95</v>
+      </c>
+      <c r="H35" t="s">
+        <v>96</v>
+      </c>
+      <c r="I35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" t="s">
+        <v>47</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.101894702048812</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.00498026007585355</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.101894702048812</v>
+      </c>
+      <c r="G36" t="s">
+        <v>92</v>
+      </c>
+      <c r="H36" t="s">
+        <v>96</v>
+      </c>
+      <c r="I36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37" t="s">
+        <v>47</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.501899133337645</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000614937647360519</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.501899133337645</v>
+      </c>
+      <c r="G37" t="s">
+        <v>92</v>
+      </c>
+      <c r="H37" t="s">
+        <v>93</v>
+      </c>
+      <c r="I37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38" t="s">
+        <v>47</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" t="s">
+        <v>92</v>
+      </c>
+      <c r="H38" t="s">
+        <v>93</v>
+      </c>
+      <c r="I38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" t="s">
+        <v>47</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.508449619307557</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000134313396803402</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.508449619307557</v>
+      </c>
+      <c r="G39" t="s">
+        <v>92</v>
+      </c>
+      <c r="H39" t="s">
+        <v>93</v>
+      </c>
+      <c r="I39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>49</v>
+      </c>
+      <c r="B40" t="s">
+        <v>47</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.164709262015411</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.00000000815190073725832</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.164709262015411</v>
+      </c>
+      <c r="G40" t="s">
+        <v>92</v>
+      </c>
+      <c r="H40" t="s">
+        <v>96</v>
+      </c>
+      <c r="I40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>50</v>
+      </c>
+      <c r="B41" t="s">
+        <v>47</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.75133619525538</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1.77502594301909e-220</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.75133619525538</v>
+      </c>
+      <c r="G41" t="s">
+        <v>92</v>
+      </c>
+      <c r="H41" t="s">
+        <v>93</v>
+      </c>
+      <c r="I41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" t="s">
+        <v>48</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.402521982423363</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.0000000000000000000000000000000000000000000000445193955872244</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.402521982423363</v>
+      </c>
+      <c r="G42" t="s">
+        <v>92</v>
+      </c>
+      <c r="H42" t="s">
+        <v>97</v>
+      </c>
+      <c r="I42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" t="s">
+        <v>48</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.0468050517964131</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.828200592969321</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.0468050517964131</v>
+      </c>
+      <c r="G43" t="s">
+        <v>92</v>
+      </c>
+      <c r="H43" t="s">
+        <v>94</v>
+      </c>
+      <c r="I43" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" t="s">
+        <v>48</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-0.0468050517964131</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.828200592969321</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.0468050517964131</v>
+      </c>
+      <c r="G44" t="s">
+        <v>95</v>
+      </c>
+      <c r="H44" t="s">
+        <v>94</v>
+      </c>
+      <c r="I44" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45" t="s">
+        <v>48</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.561102867268935</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000051307244016218</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.561102867268935</v>
+      </c>
+      <c r="G45" t="s">
+        <v>92</v>
+      </c>
+      <c r="H45" t="s">
+        <v>93</v>
+      </c>
+      <c r="I45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>47</v>
+      </c>
+      <c r="B46" t="s">
+        <v>48</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.508449619307557</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000295489472967485</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.508449619307557</v>
+      </c>
+      <c r="G46" t="s">
+        <v>92</v>
+      </c>
+      <c r="H46" t="s">
+        <v>93</v>
+      </c>
+      <c r="I46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>48</v>
+      </c>
+      <c r="B47" t="s">
+        <v>48</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" t="s">
+        <v>92</v>
+      </c>
+      <c r="H47" t="s">
+        <v>93</v>
+      </c>
+      <c r="I47" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>49</v>
+      </c>
+      <c r="B48" t="s">
+        <v>48</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.284589854828073</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.0000000000000000000000053595328821925</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.284589854828073</v>
+      </c>
+      <c r="G48" t="s">
+        <v>92</v>
+      </c>
+      <c r="H48" t="s">
+        <v>96</v>
+      </c>
+      <c r="I48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>50</v>
+      </c>
+      <c r="B49" t="s">
+        <v>48</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.80365185573481</v>
+      </c>
+      <c r="D49" t="n">
+        <v>8.59783131735269e-275</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.80365185573481</v>
+      </c>
+      <c r="G49" t="s">
+        <v>92</v>
+      </c>
+      <c r="H49" t="s">
+        <v>93</v>
+      </c>
+      <c r="I49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" t="s">
+        <v>49</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.0577676923179115</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.4888769390207</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.0577676923179115</v>
+      </c>
+      <c r="G50" t="s">
+        <v>92</v>
+      </c>
+      <c r="H50" t="s">
+        <v>94</v>
+      </c>
+      <c r="I50" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>44</v>
+      </c>
+      <c r="B51" t="s">
+        <v>49</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.0577599479280523</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.4888769390207</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.0577599479280523</v>
+      </c>
+      <c r="G51" t="s">
+        <v>92</v>
+      </c>
+      <c r="H51" t="s">
+        <v>94</v>
+      </c>
+      <c r="I51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>45</v>
+      </c>
+      <c r="B52" t="s">
+        <v>49</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-0.0577599479280523</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.4888769390207</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.0577599479280523</v>
+      </c>
+      <c r="G52" t="s">
+        <v>95</v>
+      </c>
+      <c r="H52" t="s">
+        <v>94</v>
+      </c>
+      <c r="I52" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>46</v>
+      </c>
+      <c r="B53" t="s">
+        <v>49</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.28597019957759</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.0000000000000000000000508284364027801</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.28597019957759</v>
+      </c>
+      <c r="G53" t="s">
+        <v>92</v>
+      </c>
+      <c r="H53" t="s">
+        <v>96</v>
+      </c>
+      <c r="I53" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>47</v>
+      </c>
+      <c r="B54" t="s">
+        <v>49</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.164709262015411</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.000000114126610321616</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.164709262015411</v>
+      </c>
+      <c r="G54" t="s">
+        <v>92</v>
+      </c>
+      <c r="H54" t="s">
+        <v>96</v>
+      </c>
+      <c r="I54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>48</v>
+      </c>
+      <c r="B55" t="s">
+        <v>49</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.284589854828073</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.0000000000000000000000803929932328874</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.284589854828073</v>
+      </c>
+      <c r="G55" t="s">
+        <v>92</v>
+      </c>
+      <c r="H55" t="s">
+        <v>96</v>
+      </c>
+      <c r="I55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>49</v>
+      </c>
+      <c r="B56" t="s">
+        <v>49</v>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" t="s">
+        <v>92</v>
+      </c>
+      <c r="H56" t="s">
+        <v>93</v>
+      </c>
+      <c r="I56" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>50</v>
+      </c>
+      <c r="B57" t="s">
+        <v>49</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.582932560347615</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000383754062864654</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.582932560347615</v>
+      </c>
+      <c r="G57" t="s">
+        <v>92</v>
+      </c>
+      <c r="H57" t="s">
+        <v>93</v>
+      </c>
+      <c r="I57" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>43</v>
+      </c>
+      <c r="B58" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.390859735670668</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.0000000000000000000000000000000000000000000332499809327093</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.390859735670668</v>
+      </c>
+      <c r="G58" t="s">
+        <v>92</v>
+      </c>
+      <c r="H58" t="s">
+        <v>97</v>
+      </c>
+      <c r="I58" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" t="s">
+        <v>50</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-0.0157149574167822</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.0157149574167822</v>
+      </c>
+      <c r="G59" t="s">
+        <v>95</v>
+      </c>
+      <c r="H59" t="s">
+        <v>94</v>
+      </c>
+      <c r="I59" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>45</v>
+      </c>
+      <c r="B60" t="s">
+        <v>50</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.0157149574167822</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.0157149574167822</v>
+      </c>
+      <c r="G60" t="s">
+        <v>92</v>
+      </c>
+      <c r="H60" t="s">
+        <v>94</v>
+      </c>
+      <c r="I60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>46</v>
+      </c>
+      <c r="B61" t="s">
+        <v>50</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.796541000136099</v>
+      </c>
+      <c r="D61" t="n">
+        <v>4.52618314836424e-265</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.796541000136099</v>
+      </c>
+      <c r="G61" t="s">
+        <v>92</v>
+      </c>
+      <c r="H61" t="s">
+        <v>93</v>
+      </c>
+      <c r="I61" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>47</v>
+      </c>
+      <c r="B62" t="s">
+        <v>50</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.75133619525538</v>
+      </c>
+      <c r="D62" t="n">
+        <v>4.43756485754771e-219</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.75133619525538</v>
+      </c>
+      <c r="G62" t="s">
+        <v>92</v>
+      </c>
+      <c r="H62" t="s">
+        <v>93</v>
+      </c>
+      <c r="I62" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>48</v>
+      </c>
+      <c r="B63" t="s">
+        <v>50</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.80365185573481</v>
+      </c>
+      <c r="D63" t="n">
+        <v>2.32141445568523e-273</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.80365185573481</v>
+      </c>
+      <c r="G63" t="s">
+        <v>92</v>
+      </c>
+      <c r="H63" t="s">
+        <v>93</v>
+      </c>
+      <c r="I63" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>49</v>
+      </c>
+      <c r="B64" t="s">
+        <v>50</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.582932560347615</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000921009750875169</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.582932560347615</v>
+      </c>
+      <c r="G64" t="s">
+        <v>92</v>
+      </c>
+      <c r="H64" t="s">
+        <v>93</v>
+      </c>
+      <c r="I64" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>50</v>
+      </c>
+      <c r="B65" t="s">
+        <v>50</v>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" t="s">
+        <v>92</v>
+      </c>
+      <c r="H65" t="s">
+        <v>93</v>
+      </c>
+      <c r="I65" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId13"/>
   </tableParts>
 </worksheet>
 </file>
@@ -927,12 +3267,14 @@
     <col min="3" max="3" width="5.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="12.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="27.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="11.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="14.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="11.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="10.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="17.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="29.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="13.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="11.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="14.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="11.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="10.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="17.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="29.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="9.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -969,10 +3311,16 @@
       <c r="K1" t="s">
         <v>21</v>
       </c>
+      <c r="L1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B2" t="n">
         <v>1211</v>
@@ -984,30 +3332,36 @@
         <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" t="n">
         <v>0.874681143514216</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>8143.4905069051</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>190</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>0.556795490374051</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>0.618750772837551</v>
+      </c>
+      <c r="M2" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B3" t="n">
         <v>1211</v>
@@ -1019,25 +3373,31 @@
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.836508465500397</v>
+        <v>25</v>
+      </c>
+      <c r="F3" t="s">
+        <v>25</v>
       </c>
       <c r="G3" t="n">
-        <v>4335.52993751679</v>
+        <v>0.836508465500292</v>
       </c>
       <c r="H3" t="n">
+        <v>4335.52993751877</v>
+      </c>
+      <c r="I3" t="n">
         <v>66</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>0.776886802110134</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>0.645536890534378</v>
+      </c>
+      <c r="M3" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1050,6 +3410,487 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="15.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="17.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="20.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="9.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2"/>
+      <c r="D2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId5"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="27.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="7.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="9.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="11.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="17.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="11.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="11.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="11.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="22.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="16.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>46</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.3678089733003</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.583912210079658</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.340953469080111</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>30</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.37314203137903</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.589878170339837</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.347956255843473</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>30</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.62685796862097</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.589878170339837</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.347956255843473</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>13</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.78364987613543</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.660984490435074</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.436900496595715</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>13</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.71043214973851</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.713642724321826</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.509285937977478</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>13</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.7608037434627</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.684836106029668</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.469000492121879</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>13</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3.56840077071291</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.664718726145348</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.441850984888294</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>40</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.70582163501239</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.500135713194276</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.250135731612347</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId6"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="8.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="7.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="9.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="11.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="17.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="4.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="3.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="8.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="22.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="16.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId7"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -1079,72 +3920,72 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B1" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C1" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="D1" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="E1" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="F1" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="G1" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="H1" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="I1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="J1" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="K1" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="L1" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="M1" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="N1" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="O1" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="P1" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="Q1" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="R1" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="S1" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="T1" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="U1" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
@@ -1209,7 +4050,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="B3" t="n">
         <v>0.267617994709331</v>
@@ -1274,7 +4115,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="B4" t="n">
         <v>0.373464240737937</v>
@@ -1339,7 +4180,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="B5" t="n">
         <v>0.00563736422623214</v>
@@ -1404,7 +4245,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B6" t="n">
         <v>0.364625906536881</v>
@@ -1469,7 +4310,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="B7" t="n">
         <v>0.245988403020073</v>
@@ -1534,7 +4375,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="B8" t="n">
         <v>0.239511243543399</v>
@@ -1599,7 +4440,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="B9" t="n">
         <v>0.438629578998608</v>
@@ -1664,7 +4505,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="B10" t="n">
         <v>0.125125645024876</v>
@@ -1729,7 +4570,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="B11" t="n">
         <v>0.191971224492248</v>
@@ -1794,7 +4635,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="B12" t="n">
         <v>0.261860125559326</v>
@@ -1859,7 +4700,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="B13" t="n">
         <v>0.282726098124659</v>
@@ -1924,7 +4765,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="B14" t="n">
         <v>-0.0909245300904354</v>
@@ -1989,7 +4830,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="B15" t="n">
         <v>0.0119088691197831</v>
@@ -2054,7 +4895,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="B16" t="n">
         <v>0.0972514888674256</v>
@@ -2119,7 +4960,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="B17" t="n">
         <v>0.0675220071367358</v>
@@ -2184,7 +5025,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="B18" t="n">
         <v>-0.00178750795550761</v>
@@ -2249,7 +5090,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="B19" t="n">
         <v>0.0306635518266179</v>
@@ -2314,7 +5155,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="B20" t="n">
         <v>-0.0642419784580394</v>
@@ -2379,7 +5220,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="B21" t="n">
         <v>-0.0400634391362532</v>
@@ -2446,12 +5287,12 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId8"/>
   </tableParts>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -2473,54 +5314,54 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B1" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="C1" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="D1" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="E1" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="F1" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="G1" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="H1" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="I1" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="J1" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="K1" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="L1" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="M1" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.149029319187789</v>
+        <v>0.149029319187779</v>
       </c>
       <c r="D2" t="n">
         <v>0.457508379926087</v>
@@ -2529,7 +5370,7 @@
         <v>0.37046900393905</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.208606849637576</v>
+        <v>0.208606849637572</v>
       </c>
       <c r="G2" t="n">
         <v>0.254798189732074</v>
@@ -2547,7 +5388,7 @@
         <v>0.242988291007562</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.0483327250702426</v>
+        <v>0.0483327250688402</v>
       </c>
       <c r="M2" t="n">
         <v>0.301937321834856</v>
@@ -2555,54 +5396,54 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.149029319187789</v>
+        <v>0.149029319187779</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.101108715934067</v>
+        <v>0.101108715933435</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.297596229813512</v>
+        <v>0.29759622981355</v>
       </c>
       <c r="F3" t="n">
-        <v>0.44754669217044</v>
+        <v>0.447546692171656</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.334793754793052</v>
+        <v>0.334793754792803</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.179940502910901</v>
+        <v>0.1799405029109</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.260895034702212</v>
+        <v>0.260895034703056</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.197714558375127</v>
+        <v>0.197714558373469</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0677116908944671</v>
+        <v>0.0677116908945005</v>
       </c>
       <c r="L3" t="n">
-        <v>0.137110609356486</v>
+        <v>0.137110609357277</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0155727366020519</v>
+        <v>0.0155727366033493</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="B4" t="n">
         <v>0.457508379926087</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.101108715934067</v>
+        <v>0.101108715933435</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -2611,7 +5452,7 @@
         <v>0.37877029683852</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.122728438923987</v>
+        <v>0.122728438924549</v>
       </c>
       <c r="G4" t="n">
         <v>0.277345063243243</v>
@@ -2629,7 +5470,7 @@
         <v>0.263935327341455</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0191271677041449</v>
+        <v>-0.0191271677041449</v>
       </c>
       <c r="M4" t="n">
         <v>0.427465359908782</v>
@@ -2637,13 +5478,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="B5" t="n">
         <v>0.37046900393905</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.297596229813512</v>
+        <v>0.29759622981355</v>
       </c>
       <c r="D5" t="n">
         <v>0.37877029683852</v>
@@ -2652,7 +5493,7 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.17690557851586</v>
+        <v>0.176905578517113</v>
       </c>
       <c r="G5" t="n">
         <v>0.645536890534378</v>
@@ -2670,7 +5511,7 @@
         <v>0.232600687812317</v>
       </c>
       <c r="L5" t="n">
-        <v>0.150197456361309</v>
+        <v>-0.150197456361309</v>
       </c>
       <c r="M5" t="n">
         <v>0.245944250456197</v>
@@ -2678,54 +5519,54 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.208606849637576</v>
+        <v>0.208606849637572</v>
       </c>
       <c r="C6" t="n">
-        <v>0.44754669217044</v>
+        <v>0.447546692171656</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.122728438923987</v>
+        <v>0.122728438924549</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.17690557851586</v>
+        <v>0.176905578517113</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.116136091513795</v>
+        <v>0.11613609151498</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.154017044241559</v>
+        <v>0.154017044240104</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0769069606457822</v>
+        <v>0.0769069606458112</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.15750918180599</v>
+        <v>0.157509181805977</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0320424677337021</v>
+        <v>0.0320424677316785</v>
       </c>
       <c r="L6" t="n">
-        <v>0.137601066955604</v>
+        <v>0.137601066954924</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0224800025089799</v>
+        <v>0.0224800025089032</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="B7" t="n">
         <v>0.254798189732074</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.334793754793052</v>
+        <v>0.334793754792803</v>
       </c>
       <c r="D7" t="n">
         <v>0.277345063243243</v>
@@ -2734,7 +5575,7 @@
         <v>0.645536890534378</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.116136091513795</v>
+        <v>0.11613609151498</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -2752,7 +5593,7 @@
         <v>0.296104876868089</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0927417103993887</v>
+        <v>-0.0927417104000216</v>
       </c>
       <c r="M7" t="n">
         <v>0.177688525862042</v>
@@ -2760,13 +5601,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="B8" t="n">
         <v>0.436182608530502</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.179940502910901</v>
+        <v>0.1799405029109</v>
       </c>
       <c r="D8" t="n">
         <v>0.57764259989121</v>
@@ -2775,7 +5616,7 @@
         <v>0.434306843583534</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.154017044241559</v>
+        <v>0.154017044240104</v>
       </c>
       <c r="G8" t="n">
         <v>0.347353111784276</v>
@@ -2793,7 +5634,7 @@
         <v>0.26453883728348</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0530016330429033</v>
+        <v>-0.0530016330437549</v>
       </c>
       <c r="M8" t="n">
         <v>0.382458081420708</v>
@@ -2801,13 +5642,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="B9" t="n">
         <v>0.32496248088319</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.260895034702212</v>
+        <v>0.260895034703056</v>
       </c>
       <c r="D9" t="n">
         <v>0.274559789588428</v>
@@ -2816,7 +5657,7 @@
         <v>0.434674594705569</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0769069606457822</v>
+        <v>0.0769069606458112</v>
       </c>
       <c r="G9" t="n">
         <v>0.479420697450724</v>
@@ -2834,7 +5675,7 @@
         <v>0.418720566432591</v>
       </c>
       <c r="L9" t="n">
-        <v>0.102630213200542</v>
+        <v>-0.10263021320123</v>
       </c>
       <c r="M9" t="n">
         <v>0.300516760604275</v>
@@ -2842,13 +5683,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="B10" t="n">
         <v>0.45089187637055</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.197714558375127</v>
+        <v>0.197714558373469</v>
       </c>
       <c r="D10" t="n">
         <v>0.489796903584521</v>
@@ -2857,7 +5698,7 @@
         <v>0.50548199651497</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.15750918180599</v>
+        <v>0.157509181805977</v>
       </c>
       <c r="G10" t="n">
         <v>0.444894111959486</v>
@@ -2875,7 +5716,7 @@
         <v>0.244372246406736</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0731501977229881</v>
+        <v>-0.0731501977229854</v>
       </c>
       <c r="M10" t="n">
         <v>0.342918718135176</v>
@@ -2883,13 +5724,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="B11" t="n">
         <v>0.242988291007562</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.0677116908944671</v>
+        <v>0.0677116908945005</v>
       </c>
       <c r="D11" t="n">
         <v>0.263935327341455</v>
@@ -2898,7 +5739,7 @@
         <v>0.232600687812317</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0320424677337021</v>
+        <v>0.0320424677316785</v>
       </c>
       <c r="G11" t="n">
         <v>0.296104876868089</v>
@@ -2916,7 +5757,7 @@
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0917246173196838</v>
+        <v>0.0917246173191038</v>
       </c>
       <c r="M11" t="n">
         <v>0.350322848366765</v>
@@ -2924,54 +5765,54 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.0483327250702426</v>
+        <v>0.0483327250688402</v>
       </c>
       <c r="C12" t="n">
-        <v>0.137110609356486</v>
+        <v>0.137110609357277</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0191271677041449</v>
+        <v>-0.0191271677041449</v>
       </c>
       <c r="E12" t="n">
-        <v>0.150197456361309</v>
+        <v>-0.150197456361309</v>
       </c>
       <c r="F12" t="n">
-        <v>0.137601066955604</v>
+        <v>0.137601066954924</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0927417103993887</v>
+        <v>-0.0927417104000216</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0530016330429033</v>
+        <v>-0.0530016330437549</v>
       </c>
       <c r="I12" t="n">
-        <v>0.102630213200542</v>
+        <v>-0.10263021320123</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0731501977229881</v>
+        <v>-0.0731501977229854</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.0917246173196838</v>
+        <v>0.0917246173191038</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.0421817110970289</v>
+        <v>0.0421817110988284</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="B13" t="n">
         <v>0.301937321834856</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.0155727366020519</v>
+        <v>0.0155727366033493</v>
       </c>
       <c r="D13" t="n">
         <v>0.427465359908782</v>
@@ -2980,7 +5821,7 @@
         <v>0.245944250456197</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0224800025089799</v>
+        <v>0.0224800025089032</v>
       </c>
       <c r="G13" t="n">
         <v>0.177688525862042</v>
@@ -2998,616 +5839,10 @@
         <v>0.350322848366765</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.0421817110970289</v>
+        <v>0.0421817110988284</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-  <tableParts count="1">
-    <tablePart r:id="rId6"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="27.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="17.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="27.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="27.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="20.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="16.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="21.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="17.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="16.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" t="s">
-        <v>64</v>
-      </c>
-      <c r="I1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-0.0422258129968075</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.822090116003482</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.249932726770631</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.480641275836943</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.402521982423363</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.245789870611451</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.491263231724979</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B3" t="n">
-        <v>-0.0422258129968075</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.534136155608582</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-0.215129457140626</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-0.0712864749510076</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-0.0468050517964131</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-0.138574421881916</v>
-      </c>
-      <c r="I3" t="n">
-        <v>-0.162979145730307</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0.822090116003482</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.534136155608582</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.0888864755470457</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.366072418709504</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.31392265435685</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.12900707046776</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.322807715812227</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B5" t="n">
-        <v>0.249932726770631</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-0.215129457140626</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.0888864755470457</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.191453717408593</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.373608718546554</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.295653468570672</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.646717388135207</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B6" t="n">
-        <v>0.480641275836943</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-0.0712864749510076</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.366072418709504</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.191453717408593</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.421764945171663</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.296192385966366</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.679939053356186</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B7" t="n">
-        <v>0.402521982423363</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-0.0468050517964131</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.31392265435685</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.373608718546554</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.421764945171663</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.400412881685803</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.791921035390237</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>64</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0.245789870611451</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-0.138574421881916</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.12900707046776</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.295653468570672</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.296192385966366</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.400412881685803</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.701572333534976</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.491263231724979</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-0.162979145730307</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.322807715812227</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.646717388135207</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.679939053356186</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.791921035390237</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.701572333534976</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-  <tableParts count="1">
-    <tablePart r:id="rId7"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="27.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="17.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="27.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="27.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="20.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="16.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="21.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="17.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="16.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" t="s">
-        <v>64</v>
-      </c>
-      <c r="I1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.20705014824233</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1.42274089719385e-296</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.0000000000000000116154441857012</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000108854760506438</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.0000000000000000000000000000000000000000000000422934258078632</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.000000000000000040287916926136</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000315719216121175</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0.141949034682831</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000647320220737097</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.000000000000342625523567185</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.0392686222478805</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.20705014824233</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.00000776286694184664</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.0000000819672930576731</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B4" t="n">
-        <v>5.08121748997804e-298</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000028144357423352</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.00784246959517455</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.000000000000000000000000000000000000016816484589351</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.000000000000000000000000000588426869016001</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.0000334111675754961</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.0000000000000000000000000000136435051826395</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B5" t="n">
-        <v>0.00000000000000000105594947142738</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.0000000000000380695026185761</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.00196061739879364</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.00000000014755606657363</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.00000000000000000000000000000000000000035311887805645</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.000000000000000000000000894854707476116</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000519723952324398</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B6" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000518356002411612</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.0130895407492935</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.00000000000000000000000000000000000000105103028683444</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.0000000000184445083217038</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000040877186536419</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.000000000000000000000000783367652610398</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000106852813860862</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B7" t="n">
-        <v>0.00000000000000000000000000000000000000000000000222596977936122</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.103525074121165</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.000000000000000000000000000042030490644</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.0000000000000000000000000000000000000000207716987092029</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000204385932682095</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.000000000000000000000000000000000000000000000136478884788587</v>
-      </c>
-      <c r="I7" t="n">
-        <v>7.82159370177913e-260</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>64</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0.0000000000000000040287916926136</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.00000129381115697444</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.00000668223351509922</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.0000000000000000000000000745712256230097</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.0000000000000000000000000602590502007998</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.00000000000000000000000000000000000000000000000758216026603264</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000104344773940802</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000143508734600534</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.0000000117096132939533</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.000000000000000000000000000000909567012175963</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000216551646801832</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000427411255443446</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.89688655621449e-261</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000401326053618469</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-  <tableParts count="1">
-    <tablePart r:id="rId8"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="8.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="5.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1211</v>
       </c>
     </row>
   </sheetData>
@@ -3625,1115 +5860,275 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="27.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="27.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="11.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="10.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="17.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="25.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="27.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="20.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="16.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="21.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="17.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="16.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="B1" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="C1" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="D1" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="E1" t="s">
-        <v>72</v>
+        <v>46</v>
+      </c>
+      <c r="F1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B2" t="s">
-        <v>58</v>
+        <v>43</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0.0422258129968075</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-0.0422258129968075</v>
       </c>
       <c r="E2" t="n">
-        <v>1211</v>
+        <v>0.290214849324628</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.386808795276402</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.402521982423363</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.0577676923179115</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.390859735670668</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B3" t="s">
-        <v>58</v>
+        <v>44</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.0422258129968075</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.0422258129968075</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.141949034682831</v>
+        <v>-1</v>
       </c>
       <c r="E3" t="n">
-        <v>1211</v>
+        <v>-0.0441310527305925</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.101894702048812</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.0468050517964131</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.0577599479280523</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-0.0157149574167822</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B4" t="s">
-        <v>58</v>
+        <v>45</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-0.0422258129968075</v>
       </c>
       <c r="C4" t="n">
-        <v>0.822090116003482</v>
+        <v>-1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.08121748997804e-298</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>1211</v>
+        <v>0.0441310527305925</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.101894702048812</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.0468050517964131</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.0577599479280523</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.0157149574167822</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B5" t="s">
-        <v>58</v>
+        <v>46</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.290214849324628</v>
       </c>
       <c r="C5" t="n">
-        <v>0.249932726770631</v>
+        <v>-0.0441310527305925</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00000000000000000105594947142738</v>
+        <v>0.0441310527305925</v>
       </c>
       <c r="E5" t="n">
-        <v>1211</v>
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.501899133337645</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.561102867268935</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.28597019957759</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.796541000136099</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B6" t="s">
-        <v>58</v>
+        <v>47</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.386808795276402</v>
       </c>
       <c r="C6" t="n">
-        <v>0.480641275836943</v>
+        <v>-0.101894702048812</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000518356002411612</v>
+        <v>0.101894702048812</v>
       </c>
       <c r="E6" t="n">
-        <v>1211</v>
+        <v>0.501899133337645</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.508449619307557</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.164709262015411</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.75133619525538</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B7" t="s">
-        <v>58</v>
+        <v>48</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.402521982423363</v>
       </c>
       <c r="C7" t="n">
-        <v>0.402521982423363</v>
+        <v>0.0468050517964131</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00000000000000000000000000000000000000000000000222596977936122</v>
+        <v>-0.0468050517964131</v>
       </c>
       <c r="E7" t="n">
-        <v>1211</v>
+        <v>0.561102867268935</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.508449619307557</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.284589854828073</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.80365185573481</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>64</v>
-      </c>
-      <c r="B8" t="s">
-        <v>58</v>
+        <v>49</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.0577676923179115</v>
       </c>
       <c r="C8" t="n">
-        <v>0.245789870611451</v>
+        <v>0.0577599479280523</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0000000000000000040287916926136</v>
+        <v>-0.0577599479280523</v>
       </c>
       <c r="E8" t="n">
-        <v>1211</v>
+        <v>0.28597019957759</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.164709262015411</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.284589854828073</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.582932560347615</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B9" t="s">
-        <v>58</v>
+        <v>50</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.390859735670668</v>
       </c>
       <c r="C9" t="n">
-        <v>0.491263231724979</v>
+        <v>-0.0157149574167822</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000143508734600534</v>
+        <v>0.0157149574167822</v>
       </c>
       <c r="E9" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>58</v>
-      </c>
-      <c r="B10" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-0.0422258129968075</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.20705014824233</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>59</v>
-      </c>
-      <c r="B11" t="s">
-        <v>59</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>60</v>
-      </c>
-      <c r="B12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.534136155608582</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000028144357423352</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>61</v>
-      </c>
-      <c r="B13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-0.215129457140626</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.0000000000000380695026185761</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>62</v>
-      </c>
-      <c r="B14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-0.0712864749510076</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.0130895407492935</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>63</v>
-      </c>
-      <c r="B15" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-0.0468050517964131</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.103525074121165</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>64</v>
-      </c>
-      <c r="B16" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-0.138574421881916</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.00000129381115697444</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>65</v>
-      </c>
-      <c r="B17" t="s">
-        <v>59</v>
-      </c>
-      <c r="C17" t="n">
-        <v>-0.162979145730307</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.0000000117096132939533</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>58</v>
-      </c>
-      <c r="B18" t="s">
-        <v>60</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.822090116003482</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1.42274089719385e-296</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>59</v>
-      </c>
-      <c r="B19" t="s">
-        <v>60</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.534136155608582</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000647320220737097</v>
-      </c>
-      <c r="E19" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>60</v>
-      </c>
-      <c r="B20" t="s">
-        <v>60</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>61</v>
-      </c>
-      <c r="B21" t="s">
-        <v>60</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.0888864755470457</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.00196061739879364</v>
-      </c>
-      <c r="E21" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>62</v>
-      </c>
-      <c r="B22" t="s">
-        <v>60</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.366072418709504</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.00000000000000000000000000000000000000105103028683444</v>
-      </c>
-      <c r="E22" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>63</v>
-      </c>
-      <c r="B23" t="s">
-        <v>60</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.31392265435685</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.000000000000000000000000000042030490644</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>64</v>
-      </c>
-      <c r="B24" t="s">
-        <v>60</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.12900707046776</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.00000668223351509922</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>65</v>
-      </c>
-      <c r="B25" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0.322807715812227</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.000000000000000000000000000000909567012175963</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>58</v>
-      </c>
-      <c r="B26" t="s">
-        <v>61</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.249932726770631</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.0000000000000000116154441857012</v>
-      </c>
-      <c r="E26" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>59</v>
-      </c>
-      <c r="B27" t="s">
-        <v>61</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-0.215129457140626</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.000000000000342625523567185</v>
-      </c>
-      <c r="E27" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>60</v>
-      </c>
-      <c r="B28" t="s">
-        <v>61</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0.0888864755470457</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.00784246959517455</v>
-      </c>
-      <c r="E28" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>61</v>
-      </c>
-      <c r="B29" t="s">
-        <v>61</v>
-      </c>
-      <c r="C29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>62</v>
-      </c>
-      <c r="B30" t="s">
-        <v>61</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0.191453717408593</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.0000000000184445083217038</v>
-      </c>
-      <c r="E30" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>63</v>
-      </c>
-      <c r="B31" t="s">
-        <v>61</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0.373608718546554</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.0000000000000000000000000000000000000000207716987092029</v>
-      </c>
-      <c r="E31" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>64</v>
-      </c>
-      <c r="B32" t="s">
-        <v>61</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0.295653468570672</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.0000000000000000000000000745712256230097</v>
-      </c>
-      <c r="E32" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>65</v>
-      </c>
-      <c r="B33" t="s">
-        <v>61</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0.646717388135207</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000216551646801832</v>
-      </c>
-      <c r="E33" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>58</v>
-      </c>
-      <c r="B34" t="s">
-        <v>62</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0.480641275836943</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000108854760506438</v>
-      </c>
-      <c r="E34" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>59</v>
-      </c>
-      <c r="B35" t="s">
-        <v>62</v>
-      </c>
-      <c r="C35" t="n">
-        <v>-0.0712864749510076</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.0392686222478805</v>
-      </c>
-      <c r="E35" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>60</v>
-      </c>
-      <c r="B36" t="s">
-        <v>62</v>
-      </c>
-      <c r="C36" t="n">
-        <v>0.366072418709504</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.000000000000000000000000000000000000016816484589351</v>
-      </c>
-      <c r="E36" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>61</v>
-      </c>
-      <c r="B37" t="s">
-        <v>62</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0.191453717408593</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.00000000014755606657363</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>62</v>
-      </c>
-      <c r="B38" t="s">
-        <v>62</v>
-      </c>
-      <c r="C38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>63</v>
-      </c>
-      <c r="B39" t="s">
-        <v>62</v>
-      </c>
-      <c r="C39" t="n">
-        <v>0.421764945171663</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000204385932682095</v>
-      </c>
-      <c r="E39" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>64</v>
-      </c>
-      <c r="B40" t="s">
-        <v>62</v>
-      </c>
-      <c r="C40" t="n">
-        <v>0.296192385966366</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0.0000000000000000000000000602590502007998</v>
-      </c>
-      <c r="E40" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>65</v>
-      </c>
-      <c r="B41" t="s">
-        <v>62</v>
-      </c>
-      <c r="C41" t="n">
-        <v>0.679939053356186</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000427411255443446</v>
-      </c>
-      <c r="E41" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>58</v>
-      </c>
-      <c r="B42" t="s">
-        <v>63</v>
-      </c>
-      <c r="C42" t="n">
-        <v>0.402521982423363</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0.0000000000000000000000000000000000000000000000422934258078632</v>
-      </c>
-      <c r="E42" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>59</v>
-      </c>
-      <c r="B43" t="s">
-        <v>63</v>
-      </c>
-      <c r="C43" t="n">
-        <v>-0.0468050517964131</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0.20705014824233</v>
-      </c>
-      <c r="E43" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>60</v>
-      </c>
-      <c r="B44" t="s">
-        <v>63</v>
-      </c>
-      <c r="C44" t="n">
-        <v>0.31392265435685</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0.000000000000000000000000000588426869016001</v>
-      </c>
-      <c r="E44" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>61</v>
-      </c>
-      <c r="B45" t="s">
-        <v>63</v>
-      </c>
-      <c r="C45" t="n">
-        <v>0.373608718546554</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0.00000000000000000000000000000000000000035311887805645</v>
-      </c>
-      <c r="E45" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>62</v>
-      </c>
-      <c r="B46" t="s">
-        <v>63</v>
-      </c>
-      <c r="C46" t="n">
-        <v>0.421764945171663</v>
-      </c>
-      <c r="D46" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000040877186536419</v>
-      </c>
-      <c r="E46" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>63</v>
-      </c>
-      <c r="B47" t="s">
-        <v>63</v>
-      </c>
-      <c r="C47" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>64</v>
-      </c>
-      <c r="B48" t="s">
-        <v>63</v>
-      </c>
-      <c r="C48" t="n">
-        <v>0.400412881685803</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0.00000000000000000000000000000000000000000000000758216026603264</v>
-      </c>
-      <c r="E48" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>65</v>
-      </c>
-      <c r="B49" t="s">
-        <v>63</v>
-      </c>
-      <c r="C49" t="n">
-        <v>0.791921035390237</v>
-      </c>
-      <c r="D49" t="n">
-        <v>2.89688655621449e-261</v>
-      </c>
-      <c r="E49" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>58</v>
-      </c>
-      <c r="B50" t="s">
-        <v>64</v>
-      </c>
-      <c r="C50" t="n">
-        <v>0.245789870611451</v>
-      </c>
-      <c r="D50" t="n">
-        <v>0.000000000000000040287916926136</v>
-      </c>
-      <c r="E50" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>59</v>
-      </c>
-      <c r="B51" t="s">
-        <v>64</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-0.138574421881916</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0.00000776286694184664</v>
-      </c>
-      <c r="E51" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>60</v>
-      </c>
-      <c r="B52" t="s">
-        <v>64</v>
-      </c>
-      <c r="C52" t="n">
-        <v>0.12900707046776</v>
-      </c>
-      <c r="D52" t="n">
-        <v>0.0000334111675754961</v>
-      </c>
-      <c r="E52" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>61</v>
-      </c>
-      <c r="B53" t="s">
-        <v>64</v>
-      </c>
-      <c r="C53" t="n">
-        <v>0.295653468570672</v>
-      </c>
-      <c r="D53" t="n">
-        <v>0.000000000000000000000000894854707476116</v>
-      </c>
-      <c r="E53" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>62</v>
-      </c>
-      <c r="B54" t="s">
-        <v>64</v>
-      </c>
-      <c r="C54" t="n">
-        <v>0.296192385966366</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0.000000000000000000000000783367652610398</v>
-      </c>
-      <c r="E54" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>63</v>
-      </c>
-      <c r="B55" t="s">
-        <v>64</v>
-      </c>
-      <c r="C55" t="n">
-        <v>0.400412881685803</v>
-      </c>
-      <c r="D55" t="n">
-        <v>0.000000000000000000000000000000000000000000000136478884788587</v>
-      </c>
-      <c r="E55" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>64</v>
-      </c>
-      <c r="B56" t="s">
-        <v>64</v>
-      </c>
-      <c r="C56" t="n">
-        <v>1</v>
-      </c>
-      <c r="D56" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>65</v>
-      </c>
-      <c r="B57" t="s">
-        <v>64</v>
-      </c>
-      <c r="C57" t="n">
-        <v>0.701572333534976</v>
-      </c>
-      <c r="D57" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000401326053618469</v>
-      </c>
-      <c r="E57" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>58</v>
-      </c>
-      <c r="B58" t="s">
-        <v>65</v>
-      </c>
-      <c r="C58" t="n">
-        <v>0.491263231724979</v>
-      </c>
-      <c r="D58" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000315719216121175</v>
-      </c>
-      <c r="E58" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>59</v>
-      </c>
-      <c r="B59" t="s">
-        <v>65</v>
-      </c>
-      <c r="C59" t="n">
-        <v>-0.162979145730307</v>
-      </c>
-      <c r="D59" t="n">
-        <v>0.0000000819672930576731</v>
-      </c>
-      <c r="E59" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>60</v>
-      </c>
-      <c r="B60" t="s">
-        <v>65</v>
-      </c>
-      <c r="C60" t="n">
-        <v>0.322807715812227</v>
-      </c>
-      <c r="D60" t="n">
-        <v>0.0000000000000000000000000000136435051826395</v>
-      </c>
-      <c r="E60" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>61</v>
-      </c>
-      <c r="B61" t="s">
-        <v>65</v>
-      </c>
-      <c r="C61" t="n">
-        <v>0.646717388135207</v>
-      </c>
-      <c r="D61" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000519723952324398</v>
-      </c>
-      <c r="E61" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>62</v>
-      </c>
-      <c r="B62" t="s">
-        <v>65</v>
-      </c>
-      <c r="C62" t="n">
-        <v>0.679939053356186</v>
-      </c>
-      <c r="D62" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000106852813860862</v>
-      </c>
-      <c r="E62" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>63</v>
-      </c>
-      <c r="B63" t="s">
-        <v>65</v>
-      </c>
-      <c r="C63" t="n">
-        <v>0.791921035390237</v>
-      </c>
-      <c r="D63" t="n">
-        <v>7.82159370177913e-260</v>
-      </c>
-      <c r="E63" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>64</v>
-      </c>
-      <c r="B64" t="s">
-        <v>65</v>
-      </c>
-      <c r="C64" t="n">
-        <v>0.701572333534976</v>
-      </c>
-      <c r="D64" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000104344773940802</v>
-      </c>
-      <c r="E64" t="n">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>65</v>
-      </c>
-      <c r="B65" t="s">
-        <v>65</v>
-      </c>
-      <c r="C65" t="n">
-        <v>1</v>
-      </c>
-      <c r="D65" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" t="n">
-        <v>1211</v>
+        <v>0.796541000136099</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.75133619525538</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.80365185573481</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.582932560347615</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4743,4 +6138,290 @@
     <tablePart r:id="rId10"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="27.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="17.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="25.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="27.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="20.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="16.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="21.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="17.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="16.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.828200592969321</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.828200592969321</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0000000000000000000000106161781624385</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.000000000000000000000000000000000000000000300024817314252</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0000000000000000000000000000000000000000000000445193955872244</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.4888769390207</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.0000000000000000000000000000000000000000000332499809327093</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.141949034682831</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.828200592969321</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.00498026007585355</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.828200592969321</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.4888769390207</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.141949034682831</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.828200592969321</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.00498026007585355</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.828200592969321</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.4888769390207</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.000000000000000000000000624481068378737</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.124809100054632</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.124809100054632</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000614937647360519</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000051307244016218</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.0000000000000000000000508284364027801</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.52618314836424e-265</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.0000000000000000000000000000000000000000000166680454063474</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.000383096928911812</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.000383096928911812</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000292827451124057</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000295489472967485</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.000000114126610321616</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.43756485754771e-219</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.00000000000000000000000000000000000000000000000222596977936122</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.103525074121165</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.103525074121165</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000223074973983556</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000134313396803402</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.0000000000000000000000803929932328874</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.32141445568523e-273</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.0444433580927909</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.0444719380127927</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.0444719380127927</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.00000000000000000000000317677727517376</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.00000000815190073725832</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.0000000000000000000000053595328821925</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000921009750875169</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.00000000000000000000000000000000000000000000174999899645839</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.584831921900787</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.584831921900787</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.74083967244778e-266</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.77502594301909e-220</v>
+      </c>
+      <c r="G9" t="n">
+        <v>8.59783131735269e-275</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000383754062864654</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId11"/>
+  </tableParts>
+</worksheet>
 </file>